--- a/datos_limpios/dicc_arg_sim_avad.xlsx
+++ b/datos_limpios/dicc_arg_sim_avad.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,12 +384,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>character</t>
+          <t>factor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0-Inf</t>
+          <t>2005, 2009, 2013, 2018</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -406,12 +406,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>character</t>
+          <t>factor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0-Inf</t>
+          <t>Mujer, Varón</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -428,12 +428,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>character</t>
+          <t>factor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0-Inf</t>
+          <t>30 a 39, 40 a 49, 50 a 59, 60 a 69, 70 a 79, 80+</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -445,7 +445,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dm2_total</t>
+          <t>dm2_prev</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -460,14 +460,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Total estimado de personas con DM tipo 2 (DM2) por autorreporte según resultados ENFR</t>
+          <t>Prevalencia estimada de personas con DM2 por autorreporte según resultados ENFR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dm2_total_se</t>
+          <t>dm2_prev_se</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -482,14 +482,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Error estándar del total estimado de personas con DM2 por autorreporte según resultados ENFR</t>
+          <t>Error estándar de la prevalencia estimada de personas con DM2 por autorreporte según resultados ENFR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dm2_prev</t>
+          <t>dm2_prev_cv</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -504,14 +504,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Prevalencia estimada de personas con DM2 por autorreporte según resultados ENFR</t>
+          <t>Coeficiente de variación de la prevalencia estimada de personas con DM2 por autorreporte según resultados ENFR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dm2_prev_se</t>
+          <t>proy_pob</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -526,14 +526,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Error estándar de la prevalencia estimada de personas con DM2 por autorreporte según resultados ENFR</t>
+          <t>Proyección poblacional según sexo y grupo etario decenal</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dm2_prev_cv</t>
+          <t>pob_est</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -548,14 +548,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Coeficiente de variación de la prevalencia estimada de personas con DM2 por autorreporte según resultados ENFR</t>
+          <t>Población estándar según sexo y grupo etario decenal según Censo Nacional 2010</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>defun_n</t>
+          <t>AVP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -570,14 +570,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Número de defunciones por DM2 para el trienio correspondiente a la ENFR</t>
+          <t>Años de vida perdidos por muerte prematura (AVP) por DM2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>defun_mean</t>
+          <t>AVP_iu_l</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,14 +592,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Defunciones promedio por DM2 para el trienio correspondiente a la ENFR</t>
+          <t>Límite inferior intervalo de incertidumbre AVP por DM2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>defun_se</t>
+          <t>AVP_iu_u</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -614,14 +614,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Error estándar de las defunciones promedio por DM2 para el trienio correspondiente a la ENFR</t>
+          <t>Límite superior intervalo de incertidumbre AVP por DM2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>proy_pob</t>
+          <t>AVP_tasa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Proyección poblacional según sexo y grupo etario decenal</t>
+          <t>Tasa AVP por DM2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pob_est</t>
+          <t>AVP_tasa_iu_l</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -658,14 +658,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Población estándar según sexo y grupo etario decenal según Censo Nacional 2010</t>
+          <t>Límite inferior intervalo de incertidumbre tasa AVP por DM2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ex</t>
+          <t>AVP_tasa_iu_u</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -680,14 +680,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Esperanza de vida a la edad X según sexo y grupo etario decenal</t>
+          <t>Límite superior intervalo de incertidumbre tasa AVP por DM2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>micro_neuropatia_p</t>
+          <t>AVD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -702,14 +702,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Peso de discapacidad ponderado para DM2 con neuropatía periférica</t>
+          <t>Años vividos con discapacidad (AVD) por DM2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>micro_retinopatia_np</t>
+          <t>AVD_iu_l</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -724,14 +724,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Peso de discapacidad ponderado para DM2 con retinopatía no proliferativa</t>
+          <t>Límite inferior intervalo de incertidumbre AVD por DM2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>micro_retinopatia_p</t>
+          <t>AVD_iu_u</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -746,14 +746,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Peso de discapacidad ponderado para DM2 con retinopatía proliferativa</t>
+          <t>Límite superior intervalo de incertidumbre AVD por DM2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>micro_disf_erectil</t>
+          <t>AVD_tasa</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -768,14 +768,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Peso de discapacidad ponderado para DM2 con disfunción eréctil</t>
+          <t>Tasa AVD por DM2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>micro_nefropatia</t>
+          <t>AVD_tasa_iu_l</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -790,14 +790,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Peso de discapacidad ponderado para DM2 con amputación</t>
+          <t>Límite inferior intervalo de incertidumbre tasa AVD por DM2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>micro_ceguera</t>
+          <t>AVD_tasa_iu_u</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -812,14 +812,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Peso de discapacidad ponderado para DM2 con ceguera</t>
+          <t>Límite superior intervalo de incertidumbre tasa AVD por DM2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>micro_amputacion</t>
+          <t>AVAD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -834,14 +834,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Peso de discapacidad ponderado para DM2 con nefropatía</t>
+          <t>Años de vida ajustados por discapacidad (AVAD) por DM2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>macro_claudicacion</t>
+          <t>AVAD_iu_l</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -856,14 +856,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Peso de discapacidad ponderado para DM2 con claudicación de miembros inferiores</t>
+          <t>Límite inferior intervalo de incertidumbre AVAD por DM2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>macro_acv</t>
+          <t>AVAD_iu_u</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -878,14 +878,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Peso de discapacidad ponderado para DM2 con ACV</t>
+          <t>Límite superior intervalo de incertidumbre AVAD por DM2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>macro_iam</t>
+          <t>AVAD_tasa</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -900,14 +900,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Peso de discapacidad ponderado para DM2 con IAM</t>
+          <t>Tasa AVAD por DM2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>macro_ic</t>
+          <t>AVAD_tasa_iu_l</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -922,14 +922,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Peso de discapacidad ponderado para DM2 con IC</t>
+          <t>Límite inferior intervalo de incertidumbre tasa AVAD por DM2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sin_complicaciones</t>
+          <t>AVAD_tasa_iu_u</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -944,14 +944,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Peso de discapacidad ponderado para DM2 sin secuelas</t>
+          <t>Límite superior intervalo de incertidumbre tasa AVAD por DM2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>total_micro</t>
+          <t>AVD_total_micro</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -966,14 +966,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Peso de discapacidad ponderado para DM2 con secuelas microvasculares</t>
+          <t>Años vividos con discapacidad (AVD) por complicaciones microvasculares de DM2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>total_macro</t>
+          <t>AVD_iu_l_total_micro</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -988,14 +988,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Peso de discapacidad ponderado para DM2 con secuelas macrovasculares</t>
+          <t>Límite inferior intervalo de incertidumbre AVD por complicaciones microvasculares de DM2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>total_compl</t>
+          <t>AVD_iu_u_total_micro</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1010,7 +1010,1789 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Peso de discapacidad ponderado para DM2 con secuelas micro y macrovasculares</t>
+          <t>Límite superior intervalo de incertidumbre AVD por complicaciones microvasculares de DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AVD_tasa_total_micro</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Tasa AVD por complicaciones microvasculares de DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_l_total_micro</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre tasa AVD por complicaciones microvasculares de DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_u_total_micro</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre tasa AVD por complicaciones microvasculares de DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AVD_total_macro</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Años vividos con discapacidad (AVD) por complicaciones macrovasculares de DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AVD_iu_l_total_macro</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre AVD por complicaciones macrovasculares de DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AVD_iu_u_total_macro</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre AVD por complicaciones macrovasculares de DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AVD_tasa_total_macro</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Tasa AVD por complicaciones macrovasculares de DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_l_total_macro</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre tasa AVD por complicaciones macrovasculares de DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_u_total_macro</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre tasa AVD por complicaciones macrovasculares de DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AVD_micro_neuropatia_p</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Años vividos con discapacidad (AVD) por neuropatía periférica asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AVD_iu_l_micro_neuropatia_p</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre AVD por neuropatía periférica asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AVD_iu_u_micro_neuropatia_p</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre AVD por neuropatía periférica asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AVD_tasa_micro_neuropatia_p</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Tasa AVD por neuropatía periférica asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_l_micro_neuropatia_p</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre tasa AVD por neuropatía periférica asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_u_micro_neuropatia_p</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre tasa AVD por neuropatía periférica asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>AVD_micro_retinopatia_np</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Años vividos con discapacidad (AVD) por retinopatía no proliferativa asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>AVD_iu_l_micro_retinopatia_np</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre AVD por retinopatía no proliferativa asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AVD_iu_u_micro_retinopatia_np</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre AVD por retinopatía no proliferativa asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AVD_tasa_micro_retinopatia_np</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Tasa AVD por retinopatía no proliferativa asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_l_micro_retinopatia_np</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre tasa AVD por retinopatía no proliferativa asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_u_micro_retinopatia_np</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre tasa AVD por retinopatía no proliferativa asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AVD_micro_retinopatia_p</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Años vividos con discapacidad (AVD) por retinopatía proliferativa asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AVD_iu_l_micro_retinopatia_p</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre AVD por retinopatía proliferativa asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AVD_iu_u_micro_retinopatia_p</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre AVD por retinopatía proliferativa asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AVD_tasa_micro_retinopatia_p</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Tasa AVD por retinopatía proliferativa asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_l_micro_retinopatia_p</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre tasa AVD por retinopatía proliferativa asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_u_micro_retinopatia_p</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre tasa AVD por retinopatía proliferativa asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AVD_micro_disf_erectil</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Años vividos con discapacidad (AVD) por disfunción eréctil asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AVD_iu_l_micro_disf_erectil</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre AVD por disfunción eréctil asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>AVD_iu_u_micro_disf_erectil</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre AVD por disfunción eréctil asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>AVD_tasa_micro_disf_erectil</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Tasa AVD por disfunción eréctil asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_l_micro_disf_erectil</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre tasa AVD por disfunción eréctil asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_u_micro_disf_erectil</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre tasa AVD por disfunción eréctil asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AVD_micro_nefropatia</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Años vividos con discapacidad (AVD) por nefropatía asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AVD_iu_l_micro_nefropatia</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre AVD por nefropatía asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>AVD_iu_u_micro_nefropatia</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre AVD por nefropatía asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>AVD_tasa_micro_nefropatia</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Tasa AVD por nefropatía asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_l_micro_nefropatia</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre tasa AVD por nefropatía asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_u_micro_nefropatia</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre tasa AVD por nefropatía asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>AVD_micro_ceguera</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Años vividos con discapacidad (AVD) por ceguera asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>AVD_iu_l_micro_ceguera</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre AVD por ceguera asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AVD_iu_u_micro_ceguera</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre AVD por ceguera asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>AVD_tasa_micro_ceguera</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Tasa AVD por ceguera asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_l_micro_ceguera</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre tasa AVD por ceguera asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_u_micro_ceguera</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre tasa AVD por ceguera asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>AVD_micro_amputacion</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Años vividos con discapacidad (AVD) por amputación asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>AVD_iu_l_micro_amputacion</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre AVD por amputación asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>AVD_iu_u_micro_amputacion</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre AVD por amputación asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>AVD_tasa_micro_amputacion</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Tasa AVD por amputación asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_l_micro_amputacion</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre tasa AVD por amputación asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_u_micro_amputacion</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre tasa AVD por amputación asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>AVD_macro_claudicacion</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Años vividos con discapacidad (AVD) por claudicación de miembros inferiores asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>AVD_iu_l_macro_claudicacion</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre AVD por claudicación de miembros inferiores asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>AVD_iu_u_macro_claudicacion</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre AVD por claudicación de miembros inferiores asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>AVD_tasa_macro_claudicacion</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Tasa AVD por claudicación de miembros inferiores asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_l_macro_claudicacion</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre tasa AVD por claudicación de miembros inferiores asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_u_macro_claudicacion</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre tasa AVD por claudicación de miembros inferiores asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>AVD_macro_acv</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Años vividos con discapacidad (AVD) por accidente cerebrovascular asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AVD_iu_l_macro_acv</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre AVD por accidente cerebrovascular asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>AVD_iu_u_macro_acv</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre AVD por accidente cerebrovascular asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>AVD_tasa_macro_acv</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Tasa AVD por accidente cerebrovascular asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_l_macro_acv</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre tasa AVD por accidente cerebrovascular asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_u_macro_acv</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre tasa AVD por accidente cerebrovascular asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AVD_macro_iam</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Años vividos con discapacidad (AVD) por infarto agudo de miocardio asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AVD_iu_l_macro_iam</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre AVD por infarto agudo de miocardio asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AVD_iu_u_macro_iam</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre AVD por infarto agudo de miocardio asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>AVD_tasa_macro_iam</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Tasa AVD por infarto agudo de miocardio asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_l_macro_iam</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre tasa AVD por infarto agudo de miocardio asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_u_macro_iam</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre tasa AVD por infarto agudo de miocardio asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AVD_macro_ic</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Años vividos con discapacidad (AVD) por insuficiencia cardíaca asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>AVD_iu_l_macro_ic</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre AVD por insuficiencia cardíaca asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AVD_iu_u_macro_ic</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre AVD por insuficiencia cardíaca asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AVD_tasa_macro_ic</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Tasa AVD por insuficiencia cardíaca asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_l_macro_ic</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre tasa AVD por insuficiencia cardíaca asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_u_macro_ic</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre tasa AVD por insuficiencia cardíaca asociada a DM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AVD_sin_complicaciones</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Años vividos con discapacidad (AVD) por DM2 sin secuelas</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AVD_iu_l_sin_complicaciones</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre AVD por DM2 sin secuelas</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AVD_iu_u_sin_complicaciones</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre AVD por DM2 sin secuelas</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AVD_tasa_sin_complicaciones</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Tasa AVD por DM2 sin secuelas</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_l_sin_complicaciones</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Límite inferior intervalo de incertidumbre tasa AVD por DM2 sin secuelas</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>AVD_tasa_iu_u_sin_complicaciones</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Límite superior intervalo de incertidumbre tasa AVD por DM2 sin secuelas</t>
         </is>
       </c>
     </row>
